--- a/experiments/results/resnet18/CIFAR-100/baseline/energy/adaptive/avg/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-100/baseline/energy/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -960,6 +960,55 @@
       <c r="O12" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=0.3,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>94.78</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>81.34</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>76.62</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>65.31999999999999</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>85.20999999999999</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>96.23999999999999</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>63.13</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=0.05,type=avg</t>
         </is>
       </c>
     </row>
